--- a/Audit.xlsx
+++ b/Audit.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="811" firstSheet="7" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260406" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260413" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260420" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260427" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260504" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260511" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260518" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260525" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="20260406" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20260413" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="20260420" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="20260427" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="20260504" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="20260511" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="20260518" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="20260525" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'20260406'!$A$1:$N$33</definedName>
@@ -657,7 +657,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -675,26 +675,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -706,7 +706,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -724,26 +724,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -755,7 +755,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -773,26 +773,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -804,7 +804,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -822,26 +822,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -853,7 +853,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -871,26 +871,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -902,7 +902,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -920,26 +920,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -951,7 +951,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -969,26 +969,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1000,7 +1000,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -1018,26 +1018,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:xfrm>
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+        <a:prstGeom prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>

--- a/Audit.xlsx
+++ b/Audit.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="811" firstSheet="7" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="20260406" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="20260413" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="20260420" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="20260427" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="20260504" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="20260511" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="20260518" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="20260525" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260406" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260413" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260420" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260427" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260504" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260511" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260518" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20260525" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'20260406'!$A$1:$N$33</definedName>
@@ -657,7 +657,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -675,26 +675,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -706,7 +706,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -724,26 +724,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -755,7 +755,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -773,26 +773,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -804,7 +804,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -822,26 +822,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -853,7 +853,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -871,26 +871,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -902,7 +902,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -920,26 +920,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -951,7 +951,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -969,26 +969,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -1000,7 +1000,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>0</col>
@@ -1018,26 +1018,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 5" descr="E:\SRM Tech\SRMTech_Logo_03Sep2020.jpg"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="5000" t="36250" r="4584" b="39166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="5000" t="36250" r="4584" b="39166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23812" y="23812"/>
           <a:ext cx="1226484" cy="301438"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
